--- a/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Indonesia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Updated Variables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E558FC0A-D17A-5746-93D9-0C6CE87C55C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFCA10B-ED5A-2F40-B8D1-C8E98DAE3E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="229">
   <si>
     <t>BPMCCS BAU Policy Mandated Capacity Construction Schedule</t>
   </si>
@@ -710,6 +710,24 @@
   <si>
     <t>Fuel Type (MW)</t>
   </si>
+  <si>
+    <t>Bioenergy</t>
+  </si>
+  <si>
+    <t>Additional capacity (MW)</t>
+  </si>
+  <si>
+    <t>Capacity in 2030</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>Capacity by 2050</t>
+  </si>
+  <si>
+    <t>Capacity up to 2050</t>
+  </si>
 </sst>
 </file>
 
@@ -1032,7 +1050,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1153,6 +1171,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="11" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1162,10 +1183,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1283,15 +1300,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>124</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>159</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1314,7 +1331,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="26581100"/>
+          <a:off x="38100" y="28194000"/>
           <a:ext cx="7645400" cy="6591300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1628,7 +1645,7 @@
       <c r="B16" s="39"/>
     </row>
     <row r="17" spans="1:2" ht="153" x14ac:dyDescent="0.2">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="63" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="55" t="s">
@@ -1636,13 +1653,13 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="187" x14ac:dyDescent="0.2">
-      <c r="A18" s="62"/>
+      <c r="A18" s="63"/>
       <c r="B18" s="55" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="221" x14ac:dyDescent="0.2">
-      <c r="A19" s="62"/>
+      <c r="A19" s="63"/>
       <c r="B19" s="55" t="s">
         <v>181</v>
       </c>
@@ -9150,40 +9167,40 @@
       </c>
     </row>
     <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="63" t="s">
+      <c r="B87" s="64" t="s">
         <v>110</v>
       </c>
-      <c r="C87" s="64"/>
-      <c r="D87" s="64"/>
-      <c r="E87" s="64"/>
-      <c r="F87" s="64"/>
-      <c r="G87" s="64"/>
-      <c r="H87" s="64"/>
-      <c r="I87" s="64"/>
-      <c r="J87" s="64"/>
-      <c r="K87" s="64"/>
-      <c r="L87" s="64"/>
-      <c r="M87" s="64"/>
-      <c r="N87" s="64"/>
-      <c r="O87" s="64"/>
-      <c r="P87" s="64"/>
-      <c r="Q87" s="64"/>
-      <c r="R87" s="64"/>
-      <c r="S87" s="64"/>
-      <c r="T87" s="64"/>
-      <c r="U87" s="64"/>
-      <c r="V87" s="64"/>
-      <c r="W87" s="64"/>
-      <c r="X87" s="64"/>
-      <c r="Y87" s="64"/>
-      <c r="Z87" s="64"/>
-      <c r="AA87" s="64"/>
-      <c r="AB87" s="64"/>
-      <c r="AC87" s="64"/>
-      <c r="AD87" s="64"/>
-      <c r="AE87" s="64"/>
-      <c r="AF87" s="64"/>
-      <c r="AG87" s="64"/>
+      <c r="C87" s="65"/>
+      <c r="D87" s="65"/>
+      <c r="E87" s="65"/>
+      <c r="F87" s="65"/>
+      <c r="G87" s="65"/>
+      <c r="H87" s="65"/>
+      <c r="I87" s="65"/>
+      <c r="J87" s="65"/>
+      <c r="K87" s="65"/>
+      <c r="L87" s="65"/>
+      <c r="M87" s="65"/>
+      <c r="N87" s="65"/>
+      <c r="O87" s="65"/>
+      <c r="P87" s="65"/>
+      <c r="Q87" s="65"/>
+      <c r="R87" s="65"/>
+      <c r="S87" s="65"/>
+      <c r="T87" s="65"/>
+      <c r="U87" s="65"/>
+      <c r="V87" s="65"/>
+      <c r="W87" s="65"/>
+      <c r="X87" s="65"/>
+      <c r="Y87" s="65"/>
+      <c r="Z87" s="65"/>
+      <c r="AA87" s="65"/>
+      <c r="AB87" s="65"/>
+      <c r="AC87" s="65"/>
+      <c r="AD87" s="65"/>
+      <c r="AE87" s="65"/>
+      <c r="AF87" s="65"/>
+      <c r="AG87" s="65"/>
       <c r="AH87" s="21"/>
     </row>
     <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9307,39 +9324,39 @@
       </c>
     </row>
     <row r="112" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="65"/>
-      <c r="C112" s="66"/>
-      <c r="D112" s="66"/>
-      <c r="E112" s="66"/>
-      <c r="F112" s="66"/>
-      <c r="G112" s="66"/>
-      <c r="H112" s="66"/>
-      <c r="I112" s="66"/>
-      <c r="J112" s="66"/>
-      <c r="K112" s="66"/>
-      <c r="L112" s="66"/>
-      <c r="M112" s="66"/>
-      <c r="N112" s="66"/>
-      <c r="O112" s="66"/>
-      <c r="P112" s="66"/>
-      <c r="Q112" s="66"/>
-      <c r="R112" s="66"/>
-      <c r="S112" s="66"/>
-      <c r="T112" s="66"/>
-      <c r="U112" s="66"/>
-      <c r="V112" s="66"/>
-      <c r="W112" s="66"/>
-      <c r="X112" s="66"/>
-      <c r="Y112" s="66"/>
-      <c r="Z112" s="66"/>
-      <c r="AA112" s="66"/>
-      <c r="AB112" s="66"/>
-      <c r="AC112" s="66"/>
-      <c r="AD112" s="66"/>
-      <c r="AE112" s="66"/>
-      <c r="AF112" s="66"/>
-      <c r="AG112" s="66"/>
-      <c r="AH112" s="66"/>
+      <c r="B112" s="66"/>
+      <c r="C112" s="67"/>
+      <c r="D112" s="67"/>
+      <c r="E112" s="67"/>
+      <c r="F112" s="67"/>
+      <c r="G112" s="67"/>
+      <c r="H112" s="67"/>
+      <c r="I112" s="67"/>
+      <c r="J112" s="67"/>
+      <c r="K112" s="67"/>
+      <c r="L112" s="67"/>
+      <c r="M112" s="67"/>
+      <c r="N112" s="67"/>
+      <c r="O112" s="67"/>
+      <c r="P112" s="67"/>
+      <c r="Q112" s="67"/>
+      <c r="R112" s="67"/>
+      <c r="S112" s="67"/>
+      <c r="T112" s="67"/>
+      <c r="U112" s="67"/>
+      <c r="V112" s="67"/>
+      <c r="W112" s="67"/>
+      <c r="X112" s="67"/>
+      <c r="Y112" s="67"/>
+      <c r="Z112" s="67"/>
+      <c r="AA112" s="67"/>
+      <c r="AB112" s="67"/>
+      <c r="AC112" s="67"/>
+      <c r="AD112" s="67"/>
+      <c r="AE112" s="67"/>
+      <c r="AF112" s="67"/>
+      <c r="AG112" s="67"/>
+      <c r="AH112" s="67"/>
     </row>
     <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -9537,39 +9554,39 @@
     <row r="306" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="307" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="308" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B308" s="65"/>
-      <c r="C308" s="66"/>
-      <c r="D308" s="66"/>
-      <c r="E308" s="66"/>
-      <c r="F308" s="66"/>
-      <c r="G308" s="66"/>
-      <c r="H308" s="66"/>
-      <c r="I308" s="66"/>
-      <c r="J308" s="66"/>
-      <c r="K308" s="66"/>
-      <c r="L308" s="66"/>
-      <c r="M308" s="66"/>
-      <c r="N308" s="66"/>
-      <c r="O308" s="66"/>
-      <c r="P308" s="66"/>
-      <c r="Q308" s="66"/>
-      <c r="R308" s="66"/>
-      <c r="S308" s="66"/>
-      <c r="T308" s="66"/>
-      <c r="U308" s="66"/>
-      <c r="V308" s="66"/>
-      <c r="W308" s="66"/>
-      <c r="X308" s="66"/>
-      <c r="Y308" s="66"/>
-      <c r="Z308" s="66"/>
-      <c r="AA308" s="66"/>
-      <c r="AB308" s="66"/>
-      <c r="AC308" s="66"/>
-      <c r="AD308" s="66"/>
-      <c r="AE308" s="66"/>
-      <c r="AF308" s="66"/>
-      <c r="AG308" s="66"/>
-      <c r="AH308" s="66"/>
+      <c r="B308" s="66"/>
+      <c r="C308" s="67"/>
+      <c r="D308" s="67"/>
+      <c r="E308" s="67"/>
+      <c r="F308" s="67"/>
+      <c r="G308" s="67"/>
+      <c r="H308" s="67"/>
+      <c r="I308" s="67"/>
+      <c r="J308" s="67"/>
+      <c r="K308" s="67"/>
+      <c r="L308" s="67"/>
+      <c r="M308" s="67"/>
+      <c r="N308" s="67"/>
+      <c r="O308" s="67"/>
+      <c r="P308" s="67"/>
+      <c r="Q308" s="67"/>
+      <c r="R308" s="67"/>
+      <c r="S308" s="67"/>
+      <c r="T308" s="67"/>
+      <c r="U308" s="67"/>
+      <c r="V308" s="67"/>
+      <c r="W308" s="67"/>
+      <c r="X308" s="67"/>
+      <c r="Y308" s="67"/>
+      <c r="Z308" s="67"/>
+      <c r="AA308" s="67"/>
+      <c r="AB308" s="67"/>
+      <c r="AC308" s="67"/>
+      <c r="AD308" s="67"/>
+      <c r="AE308" s="67"/>
+      <c r="AF308" s="67"/>
+      <c r="AG308" s="67"/>
+      <c r="AH308" s="67"/>
     </row>
     <row r="309" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="310" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -14095,7 +14112,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F61F51-0557-B84F-8418-AD541DD3D156}">
-  <dimension ref="A1:BB116"/>
+  <dimension ref="A1:BB126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="69.6640625" customWidth="1"/>
@@ -15423,108 +15440,128 @@
         <v>141</v>
       </c>
       <c r="B46" s="61">
-        <f>$F$111</f>
-        <v>1161.2727272727273</v>
+        <f>$F$111/31</f>
+        <v>37.460410557184751</v>
       </c>
       <c r="C46" s="61">
-        <f t="shared" ref="C46:L46" si="3">$F$111</f>
-        <v>1161.2727272727273</v>
+        <f t="shared" ref="C46:AF46" si="3">$F$111/31</f>
+        <v>37.460410557184751</v>
       </c>
       <c r="D46" s="61">
         <f t="shared" si="3"/>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="E46" s="61">
         <f t="shared" si="3"/>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="F46" s="61">
         <f t="shared" si="3"/>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="G46" s="61">
         <f t="shared" si="3"/>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="H46" s="61">
         <f t="shared" si="3"/>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="I46" s="61">
         <f t="shared" si="3"/>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="J46" s="61">
         <f t="shared" si="3"/>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="K46" s="61">
         <f t="shared" si="3"/>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="L46" s="61">
         <f t="shared" si="3"/>
-        <v>1161.2727272727273</v>
-      </c>
-      <c r="M46" s="43">
-        <v>0</v>
-      </c>
-      <c r="N46" s="43">
-        <v>0</v>
-      </c>
-      <c r="O46" s="43">
-        <v>0</v>
-      </c>
-      <c r="P46" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="43">
-        <v>0</v>
-      </c>
-      <c r="R46" s="43">
-        <v>0</v>
-      </c>
-      <c r="S46" s="43">
-        <v>0</v>
-      </c>
-      <c r="T46" s="43">
-        <v>0</v>
-      </c>
-      <c r="U46" s="43">
-        <v>0</v>
-      </c>
-      <c r="V46" s="43">
-        <v>0</v>
-      </c>
-      <c r="W46" s="43">
-        <v>0</v>
-      </c>
-      <c r="X46" s="43">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="43">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="43">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="43">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="43">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="43">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="43">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="43">
-        <v>0</v>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="M46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="N46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="O46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="P46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="Q46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="R46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="S46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="T46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="U46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="V46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="W46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="X46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="Y46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="Z46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="AA46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="AB46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="AC46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="AD46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="AE46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
+      </c>
+      <c r="AF46" s="61">
+        <f t="shared" si="3"/>
+        <v>37.460410557184751</v>
       </c>
       <c r="AG46" s="43">
         <v>0</v>
@@ -15592,108 +15629,128 @@
         <v>142</v>
       </c>
       <c r="B47" s="61">
-        <f>$F$112</f>
-        <v>197.72727272727272</v>
+        <f>$F$112/31</f>
+        <v>6.3782991202346038</v>
       </c>
       <c r="C47" s="61">
-        <f t="shared" ref="C47:L47" si="4">$F$112</f>
-        <v>197.72727272727272</v>
+        <f t="shared" ref="C47:AF47" si="4">$F$112/31</f>
+        <v>6.3782991202346038</v>
       </c>
       <c r="D47" s="61">
         <f t="shared" si="4"/>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="E47" s="61">
         <f t="shared" si="4"/>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="F47" s="61">
         <f t="shared" si="4"/>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="G47" s="61">
         <f t="shared" si="4"/>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="H47" s="61">
         <f t="shared" si="4"/>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="I47" s="61">
         <f t="shared" si="4"/>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="J47" s="61">
         <f t="shared" si="4"/>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="K47" s="61">
         <f t="shared" si="4"/>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="L47" s="61">
         <f t="shared" si="4"/>
-        <v>197.72727272727272</v>
-      </c>
-      <c r="M47" s="43">
-        <v>0</v>
-      </c>
-      <c r="N47" s="43">
-        <v>0</v>
-      </c>
-      <c r="O47" s="43">
-        <v>0</v>
-      </c>
-      <c r="P47" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="43">
-        <v>0</v>
-      </c>
-      <c r="R47" s="43">
-        <v>0</v>
-      </c>
-      <c r="S47" s="43">
-        <v>0</v>
-      </c>
-      <c r="T47" s="43">
-        <v>0</v>
-      </c>
-      <c r="U47" s="43">
-        <v>0</v>
-      </c>
-      <c r="V47" s="43">
-        <v>0</v>
-      </c>
-      <c r="W47" s="43">
-        <v>0</v>
-      </c>
-      <c r="X47" s="43">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="43">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="43">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="43">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="43">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="43">
-        <v>0</v>
-      </c>
-      <c r="AE47" s="43">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="43">
-        <v>0</v>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="M47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="N47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="O47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="P47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="Q47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="R47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="S47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="T47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="U47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="V47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="W47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="X47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="Y47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="Z47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="AA47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="AB47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="AC47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="AD47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="AE47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
+      </c>
+      <c r="AF47" s="61">
+        <f t="shared" si="4"/>
+        <v>6.3782991202346038</v>
       </c>
       <c r="AG47" s="43">
         <v>0</v>
@@ -15919,108 +15976,128 @@
         <v>144</v>
       </c>
       <c r="B49" s="61">
-        <f>$F$113</f>
-        <v>944.27272727272725</v>
+        <f>$E$120/31</f>
+        <v>806.45161290322585</v>
       </c>
       <c r="C49" s="61">
-        <f t="shared" ref="C49:L49" si="5">$F$113</f>
-        <v>944.27272727272725</v>
+        <f t="shared" ref="C49:AF49" si="5">$E$120/31</f>
+        <v>806.45161290322585</v>
       </c>
       <c r="D49" s="61">
         <f t="shared" si="5"/>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="E49" s="61">
         <f t="shared" si="5"/>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="F49" s="61">
         <f t="shared" si="5"/>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="G49" s="61">
         <f t="shared" si="5"/>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="H49" s="61">
         <f t="shared" si="5"/>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="I49" s="61">
         <f t="shared" si="5"/>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="J49" s="61">
         <f t="shared" si="5"/>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="K49" s="61">
         <f t="shared" si="5"/>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="L49" s="61">
         <f t="shared" si="5"/>
-        <v>944.27272727272725</v>
-      </c>
-      <c r="M49" s="43">
-        <v>0</v>
-      </c>
-      <c r="N49" s="43">
-        <v>0</v>
-      </c>
-      <c r="O49" s="43">
-        <v>0</v>
-      </c>
-      <c r="P49" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="43">
-        <v>0</v>
-      </c>
-      <c r="R49" s="43">
-        <v>0</v>
-      </c>
-      <c r="S49" s="43">
-        <v>0</v>
-      </c>
-      <c r="T49" s="43">
-        <v>0</v>
-      </c>
-      <c r="U49" s="43">
-        <v>0</v>
-      </c>
-      <c r="V49" s="43">
-        <v>0</v>
-      </c>
-      <c r="W49" s="43">
-        <v>0</v>
-      </c>
-      <c r="X49" s="43">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="43">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="43">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="43">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="43">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="43">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="43">
-        <v>0</v>
-      </c>
-      <c r="AF49" s="43">
-        <v>0</v>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="M49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="N49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="O49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="P49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="Q49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="R49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="S49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="T49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="U49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="V49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="W49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="X49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="Y49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="Z49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="AA49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="AB49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="AC49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="AD49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="AE49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
+      </c>
+      <c r="AF49" s="61">
+        <f t="shared" si="5"/>
+        <v>806.45161290322585</v>
       </c>
       <c r="AG49" s="43">
         <v>0</v>
@@ -16088,108 +16165,128 @@
         <v>145</v>
       </c>
       <c r="B50" s="61">
-        <f>$D$98</f>
-        <v>3.8061870792883794</v>
+        <f>$E$122/31</f>
+        <v>483.87096774193549</v>
       </c>
       <c r="C50" s="61">
-        <f t="shared" ref="C50:L50" si="6">$D$98</f>
-        <v>3.8061870792883794</v>
+        <f t="shared" ref="C50:AF50" si="6">$E$122/31</f>
+        <v>483.87096774193549</v>
       </c>
       <c r="D50" s="61">
         <f t="shared" si="6"/>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="E50" s="61">
         <f t="shared" si="6"/>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="F50" s="61">
         <f t="shared" si="6"/>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="G50" s="61">
         <f t="shared" si="6"/>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="H50" s="61">
         <f t="shared" si="6"/>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="I50" s="61">
         <f t="shared" si="6"/>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="J50" s="61">
         <f t="shared" si="6"/>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="K50" s="61">
         <f t="shared" si="6"/>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="L50" s="61">
         <f t="shared" si="6"/>
-        <v>3.8061870792883794</v>
-      </c>
-      <c r="M50" s="43">
-        <v>0</v>
-      </c>
-      <c r="N50" s="43">
-        <v>0</v>
-      </c>
-      <c r="O50" s="43">
-        <v>0</v>
-      </c>
-      <c r="P50" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="43">
-        <v>0</v>
-      </c>
-      <c r="R50" s="43">
-        <v>0</v>
-      </c>
-      <c r="S50" s="43">
-        <v>0</v>
-      </c>
-      <c r="T50" s="43">
-        <v>0</v>
-      </c>
-      <c r="U50" s="43">
-        <v>0</v>
-      </c>
-      <c r="V50" s="43">
-        <v>0</v>
-      </c>
-      <c r="W50" s="43">
-        <v>0</v>
-      </c>
-      <c r="X50" s="43">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="43">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="43">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="43">
-        <v>0</v>
-      </c>
-      <c r="AB50" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC50" s="43">
-        <v>0</v>
-      </c>
-      <c r="AD50" s="43">
-        <v>0</v>
-      </c>
-      <c r="AE50" s="43">
-        <v>0</v>
-      </c>
-      <c r="AF50" s="43">
-        <v>0</v>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="M50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="N50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="O50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="P50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="Q50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="R50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="S50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="T50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="U50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="V50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="W50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="X50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="Y50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="Z50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="AA50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="AB50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="AC50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="AD50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="AE50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
+      </c>
+      <c r="AF50" s="61">
+        <f t="shared" si="6"/>
+        <v>483.87096774193549</v>
       </c>
       <c r="AG50" s="43">
         <v>0</v>
@@ -16257,108 +16354,128 @@
         <v>146</v>
       </c>
       <c r="B51" s="61">
-        <f>$F$115</f>
-        <v>413.0554545454545</v>
+        <f>$E$121/31</f>
+        <v>870.9677419354839</v>
       </c>
       <c r="C51" s="61">
-        <f t="shared" ref="C51:L51" si="7">$F$115</f>
-        <v>413.0554545454545</v>
+        <f t="shared" ref="C51:AF51" si="7">$E$121/31</f>
+        <v>870.9677419354839</v>
       </c>
       <c r="D51" s="61">
         <f t="shared" si="7"/>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="E51" s="61">
         <f t="shared" si="7"/>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="F51" s="61">
         <f t="shared" si="7"/>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="G51" s="61">
         <f t="shared" si="7"/>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="H51" s="61">
         <f t="shared" si="7"/>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="I51" s="61">
         <f t="shared" si="7"/>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" si="7"/>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="K51" s="61">
         <f t="shared" si="7"/>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="L51" s="61">
         <f t="shared" si="7"/>
-        <v>413.0554545454545</v>
-      </c>
-      <c r="M51" s="43">
-        <v>0</v>
-      </c>
-      <c r="N51" s="43">
-        <v>0</v>
-      </c>
-      <c r="O51" s="43">
-        <v>0</v>
-      </c>
-      <c r="P51" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="43">
-        <v>0</v>
-      </c>
-      <c r="R51" s="43">
-        <v>0</v>
-      </c>
-      <c r="S51" s="43">
-        <v>0</v>
-      </c>
-      <c r="T51" s="43">
-        <v>0</v>
-      </c>
-      <c r="U51" s="43">
-        <v>0</v>
-      </c>
-      <c r="V51" s="43">
-        <v>0</v>
-      </c>
-      <c r="W51" s="43">
-        <v>0</v>
-      </c>
-      <c r="X51" s="43">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="43">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="43">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="43">
-        <v>0</v>
-      </c>
-      <c r="AB51" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC51" s="43">
-        <v>0</v>
-      </c>
-      <c r="AD51" s="43">
-        <v>0</v>
-      </c>
-      <c r="AE51" s="43">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="43">
-        <v>0</v>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="M51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="N51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="O51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="P51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="Q51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="R51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="S51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="T51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="U51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="V51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="W51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="X51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="Y51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="Z51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="AA51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="AB51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="AC51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="AD51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="AE51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
+      </c>
+      <c r="AF51" s="61">
+        <f t="shared" si="7"/>
+        <v>870.9677419354839</v>
       </c>
       <c r="AG51" s="43">
         <v>0</v>
@@ -16584,108 +16701,128 @@
         <v>148</v>
       </c>
       <c r="B53" s="61">
-        <f>$D$99</f>
-        <v>79.997655303170703</v>
+        <f>$D$99/31</f>
+        <v>2.5805695259087322</v>
       </c>
       <c r="C53" s="61">
-        <f t="shared" ref="C53:L53" si="8">$D$99</f>
-        <v>79.997655303170703</v>
+        <f t="shared" ref="C53:AF53" si="8">$D$99/31</f>
+        <v>2.5805695259087322</v>
       </c>
       <c r="D53" s="61">
         <f t="shared" si="8"/>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="E53" s="61">
         <f t="shared" si="8"/>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="F53" s="61">
         <f t="shared" si="8"/>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="G53" s="61">
         <f t="shared" si="8"/>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="H53" s="61">
         <f t="shared" si="8"/>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="I53" s="61">
         <f t="shared" si="8"/>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="J53" s="61">
         <f t="shared" si="8"/>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="K53" s="61">
         <f t="shared" si="8"/>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="L53" s="61">
         <f t="shared" si="8"/>
-        <v>79.997655303170703</v>
-      </c>
-      <c r="M53" s="43">
-        <v>0</v>
-      </c>
-      <c r="N53" s="43">
-        <v>0</v>
-      </c>
-      <c r="O53" s="43">
-        <v>0</v>
-      </c>
-      <c r="P53" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="43">
-        <v>0</v>
-      </c>
-      <c r="R53" s="43">
-        <v>0</v>
-      </c>
-      <c r="S53" s="43">
-        <v>0</v>
-      </c>
-      <c r="T53" s="43">
-        <v>0</v>
-      </c>
-      <c r="U53" s="43">
-        <v>0</v>
-      </c>
-      <c r="V53" s="43">
-        <v>0</v>
-      </c>
-      <c r="W53" s="43">
-        <v>0</v>
-      </c>
-      <c r="X53" s="43">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="43">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="43">
-        <v>0</v>
-      </c>
-      <c r="AA53" s="43">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="43">
-        <v>0</v>
-      </c>
-      <c r="AD53" s="43">
-        <v>0</v>
-      </c>
-      <c r="AE53" s="43">
-        <v>0</v>
-      </c>
-      <c r="AF53" s="43">
-        <v>0</v>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="M53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="N53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="O53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="P53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="Q53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="R53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="S53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="T53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="U53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="V53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="W53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="X53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="Y53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="Z53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="AA53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="AB53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="AC53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="AD53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="AE53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
+      </c>
+      <c r="AF53" s="61">
+        <f t="shared" si="8"/>
+        <v>2.5805695259087322</v>
       </c>
       <c r="AG53" s="43">
         <v>0</v>
@@ -16753,108 +16890,128 @@
         <v>149</v>
       </c>
       <c r="B54" s="61">
-        <f>$F$114</f>
-        <v>305</v>
+        <f>$F$114/31</f>
+        <v>9.8387096774193541</v>
       </c>
       <c r="C54" s="61">
-        <f t="shared" ref="C54:L54" si="9">$F$114</f>
-        <v>305</v>
+        <f t="shared" ref="C54:AF54" si="9">$F$114/31</f>
+        <v>9.8387096774193541</v>
       </c>
       <c r="D54" s="61">
         <f t="shared" si="9"/>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="E54" s="61">
         <f t="shared" si="9"/>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="F54" s="61">
         <f t="shared" si="9"/>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="G54" s="61">
         <f t="shared" si="9"/>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="H54" s="61">
         <f t="shared" si="9"/>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="I54" s="61">
         <f t="shared" si="9"/>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="9"/>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="K54" s="61">
         <f t="shared" si="9"/>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="L54" s="61">
         <f t="shared" si="9"/>
-        <v>305</v>
-      </c>
-      <c r="M54" s="43">
-        <v>0</v>
-      </c>
-      <c r="N54" s="43">
-        <v>0</v>
-      </c>
-      <c r="O54" s="43">
-        <v>0</v>
-      </c>
-      <c r="P54" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="43">
-        <v>0</v>
-      </c>
-      <c r="R54" s="43">
-        <v>0</v>
-      </c>
-      <c r="S54" s="43">
-        <v>0</v>
-      </c>
-      <c r="T54" s="43">
-        <v>0</v>
-      </c>
-      <c r="U54" s="43">
-        <v>0</v>
-      </c>
-      <c r="V54" s="43">
-        <v>0</v>
-      </c>
-      <c r="W54" s="43">
-        <v>0</v>
-      </c>
-      <c r="X54" s="43">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="43">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="43">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="43">
-        <v>0</v>
-      </c>
-      <c r="AB54" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC54" s="43">
-        <v>0</v>
-      </c>
-      <c r="AD54" s="43">
-        <v>0</v>
-      </c>
-      <c r="AE54" s="43">
-        <v>0</v>
-      </c>
-      <c r="AF54" s="43">
-        <v>0</v>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="M54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="N54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="O54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="P54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="Q54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="R54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="S54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="T54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="U54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="V54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="W54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="X54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="Y54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="Z54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="AA54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="AB54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="AC54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="AD54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="AE54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
+      </c>
+      <c r="AF54" s="61">
+        <f t="shared" si="9"/>
+        <v>9.8387096774193541</v>
       </c>
       <c r="AG54" s="43">
         <v>0</v>
@@ -17870,108 +18027,128 @@
         <v>156</v>
       </c>
       <c r="B61" s="61">
-        <f>$D$100</f>
-        <v>0.91143560592020501</v>
+        <f>$D$100/31</f>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="C61" s="61">
-        <f t="shared" ref="C61:L61" si="10">$D$100</f>
-        <v>0.91143560592020501</v>
+        <f t="shared" ref="C61:AF61" si="10">$D$100/31</f>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="D61" s="61">
         <f t="shared" si="10"/>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="E61" s="61">
         <f t="shared" si="10"/>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="F61" s="61">
         <f t="shared" si="10"/>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="G61" s="61">
         <f t="shared" si="10"/>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="H61" s="61">
         <f t="shared" si="10"/>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="I61" s="61">
         <f t="shared" si="10"/>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="10"/>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="K61" s="61">
         <f t="shared" si="10"/>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="L61" s="61">
         <f t="shared" si="10"/>
-        <v>0.91143560592020501</v>
-      </c>
-      <c r="M61" s="43">
-        <v>0</v>
-      </c>
-      <c r="N61" s="43">
-        <v>0</v>
-      </c>
-      <c r="O61" s="43">
-        <v>0</v>
-      </c>
-      <c r="P61" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="43">
-        <v>0</v>
-      </c>
-      <c r="R61" s="43">
-        <v>0</v>
-      </c>
-      <c r="S61" s="43">
-        <v>0</v>
-      </c>
-      <c r="T61" s="43">
-        <v>0</v>
-      </c>
-      <c r="U61" s="43">
-        <v>0</v>
-      </c>
-      <c r="V61" s="43">
-        <v>0</v>
-      </c>
-      <c r="W61" s="43">
-        <v>0</v>
-      </c>
-      <c r="X61" s="43">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="43">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="43">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="43">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="43">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="43">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="43">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="43">
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="M61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="N61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="O61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="P61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="Q61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="R61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="S61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="T61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="U61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="V61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="W61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="X61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="Y61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="Z61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="AA61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="AB61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="AC61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="AD61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="AE61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
+      </c>
+      <c r="AF61" s="61">
+        <f t="shared" si="10"/>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="AG61" s="43">
         <v>0</v>
@@ -19169,7 +19346,7 @@
       <c r="C110">
         <v>2030</v>
       </c>
-      <c r="D110" s="67" t="s">
+      <c r="D110" s="62" t="s">
         <v>219</v>
       </c>
       <c r="E110" s="22" t="s">
@@ -19193,7 +19370,7 @@
         <f>C111-B111</f>
         <v>12774</v>
       </c>
-      <c r="E111" s="68">
+      <c r="E111">
         <v>11</v>
       </c>
       <c r="F111" s="56">
@@ -19302,6 +19479,135 @@
       <c r="F116" s="56">
         <f t="shared" si="16"/>
         <v>80.909090909090907</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="B119" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="C119" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="D119" s="47" t="s">
+        <v>226</v>
+      </c>
+      <c r="E119" s="47" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="B120" s="56">
+        <f>C113</f>
+        <v>15565</v>
+      </c>
+      <c r="C120" s="56">
+        <v>25000</v>
+      </c>
+      <c r="D120" s="56">
+        <f>C120-B120</f>
+        <v>9435</v>
+      </c>
+      <c r="E120" s="56">
+        <f>B120+D120</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="B121" s="56">
+        <f>C115</f>
+        <v>4680</v>
+      </c>
+      <c r="C121" s="56">
+        <v>27000</v>
+      </c>
+      <c r="D121" s="56">
+        <f>C121-B121</f>
+        <v>22320</v>
+      </c>
+      <c r="E121" s="56">
+        <f t="shared" ref="E121:E123" si="17">B121+D121</f>
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B122" s="56">
+        <f>D98</f>
+        <v>3.8061870792883794</v>
+      </c>
+      <c r="C122" s="56">
+        <v>15000</v>
+      </c>
+      <c r="D122" s="56">
+        <f>C122-B122</f>
+        <v>14996.193812920712</v>
+      </c>
+      <c r="E122" s="56">
+        <f t="shared" si="17"/>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B123" s="56">
+        <f>C114</f>
+        <v>5798</v>
+      </c>
+      <c r="C123" s="56">
+        <v>7000</v>
+      </c>
+      <c r="D123" s="56">
+        <f>C123-B123</f>
+        <v>1202</v>
+      </c>
+      <c r="E123" s="56">
+        <f t="shared" si="17"/>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="C124" s="56">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A125" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B125" s="56">
+        <f>C111</f>
+        <v>44726</v>
+      </c>
+      <c r="C125" s="56">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A126" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="B126" s="56">
+        <f>C112</f>
+        <v>25613</v>
+      </c>
+      <c r="C126" s="56">
+        <v>22000</v>
       </c>
     </row>
   </sheetData>
@@ -19512,127 +19818,127 @@
       </c>
       <c r="B2" s="43">
         <f>'Fuel Type'!B46</f>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="C2" s="43">
         <f>'Fuel Type'!C46</f>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="D2" s="43">
         <f>'Fuel Type'!D46</f>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="E2" s="43">
         <f>'Fuel Type'!E46</f>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="F2" s="43">
         <f>'Fuel Type'!F46</f>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="G2" s="43">
         <f>'Fuel Type'!G46</f>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="H2" s="43">
         <f>'Fuel Type'!H46</f>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="I2" s="43">
         <f>'Fuel Type'!I46</f>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="J2" s="43">
         <f>'Fuel Type'!J46</f>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="K2" s="43">
         <f>'Fuel Type'!K46</f>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="L2" s="43">
         <f>'Fuel Type'!L46</f>
-        <v>1161.2727272727273</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="M2" s="43">
         <f>'Fuel Type'!M46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="N2" s="43">
         <f>'Fuel Type'!N46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="O2" s="43">
         <f>'Fuel Type'!O46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="P2" s="43">
         <f>'Fuel Type'!P46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="Q2" s="43">
         <f>'Fuel Type'!Q46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="R2" s="43">
         <f>'Fuel Type'!R46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="S2" s="43">
         <f>'Fuel Type'!S46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="T2" s="43">
         <f>'Fuel Type'!T46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="U2" s="43">
         <f>'Fuel Type'!U46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="V2" s="43">
         <f>'Fuel Type'!V46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="W2" s="43">
         <f>'Fuel Type'!W46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="X2" s="43">
         <f>'Fuel Type'!X46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="Y2" s="43">
         <f>'Fuel Type'!Y46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="Z2" s="43">
         <f>'Fuel Type'!Z46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="AA2" s="43">
         <f>'Fuel Type'!AA46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="AB2" s="43">
         <f>'Fuel Type'!AB46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="AC2" s="43">
         <f>'Fuel Type'!AC46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="AD2" s="43">
         <f>'Fuel Type'!AD46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="AE2" s="43">
         <f>'Fuel Type'!AE46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="AF2" s="43">
         <f>'Fuel Type'!AF46</f>
-        <v>0</v>
+        <v>37.460410557184751</v>
       </c>
       <c r="AG2" s="43">
         <f>'Fuel Type'!AG46</f>
@@ -19721,127 +20027,127 @@
       </c>
       <c r="B3" s="43">
         <f>'Fuel Type'!B47</f>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="C3" s="43">
         <f>'Fuel Type'!C47</f>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="D3" s="43">
         <f>'Fuel Type'!D47</f>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="E3" s="43">
         <f>'Fuel Type'!E47</f>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="F3" s="43">
         <f>'Fuel Type'!F47</f>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="G3" s="43">
         <f>'Fuel Type'!G47</f>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="H3" s="43">
         <f>'Fuel Type'!H47</f>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="I3" s="43">
         <f>'Fuel Type'!I47</f>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="J3" s="43">
         <f>'Fuel Type'!J47</f>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="K3" s="43">
         <f>'Fuel Type'!K47</f>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="L3" s="43">
         <f>'Fuel Type'!L47</f>
-        <v>197.72727272727272</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="M3" s="43">
         <f>'Fuel Type'!M47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="N3" s="43">
         <f>'Fuel Type'!N47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="O3" s="43">
         <f>'Fuel Type'!O47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="P3" s="43">
         <f>'Fuel Type'!P47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="Q3" s="43">
         <f>'Fuel Type'!Q47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="R3" s="43">
         <f>'Fuel Type'!R47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="S3" s="43">
         <f>'Fuel Type'!S47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="T3" s="43">
         <f>'Fuel Type'!T47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="U3" s="43">
         <f>'Fuel Type'!U47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="V3" s="43">
         <f>'Fuel Type'!V47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="W3" s="43">
         <f>'Fuel Type'!W47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="X3" s="43">
         <f>'Fuel Type'!X47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="Y3" s="43">
         <f>'Fuel Type'!Y47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="Z3" s="43">
         <f>'Fuel Type'!Z47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="AA3" s="43">
         <f>'Fuel Type'!AA47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="AB3" s="43">
         <f>'Fuel Type'!AB47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="AC3" s="43">
         <f>'Fuel Type'!AC47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="AD3" s="43">
         <f>'Fuel Type'!AD47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="AE3" s="43">
         <f>'Fuel Type'!AE47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="AF3" s="43">
         <f>'Fuel Type'!AF47</f>
-        <v>0</v>
+        <v>6.3782991202346038</v>
       </c>
       <c r="AG3" s="43">
         <f>'Fuel Type'!AG47</f>
@@ -20128,127 +20434,127 @@
       </c>
       <c r="B5" s="43">
         <f>'Fuel Type'!B49</f>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="C5" s="43">
         <f>'Fuel Type'!C49</f>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="D5" s="43">
         <f>'Fuel Type'!D49</f>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="E5" s="43">
         <f>'Fuel Type'!E49</f>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="F5" s="43">
         <f>'Fuel Type'!F49</f>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="G5" s="43">
         <f>'Fuel Type'!G49</f>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="H5" s="43">
         <f>'Fuel Type'!H49</f>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="I5" s="43">
         <f>'Fuel Type'!I49</f>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="J5" s="43">
         <f>'Fuel Type'!J49</f>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="K5" s="43">
         <f>'Fuel Type'!K49</f>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="L5" s="43">
         <f>'Fuel Type'!L49</f>
-        <v>944.27272727272725</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="M5" s="43">
         <f>'Fuel Type'!M49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="N5" s="43">
         <f>'Fuel Type'!N49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="O5" s="43">
         <f>'Fuel Type'!O49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="P5" s="43">
         <f>'Fuel Type'!P49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="Q5" s="43">
         <f>'Fuel Type'!Q49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="R5" s="43">
         <f>'Fuel Type'!R49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="S5" s="43">
         <f>'Fuel Type'!S49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="T5" s="43">
         <f>'Fuel Type'!T49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="U5" s="43">
         <f>'Fuel Type'!U49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="V5" s="43">
         <f>'Fuel Type'!V49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="W5" s="43">
         <f>'Fuel Type'!W49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="X5" s="43">
         <f>'Fuel Type'!X49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="Y5" s="43">
         <f>'Fuel Type'!Y49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="Z5" s="43">
         <f>'Fuel Type'!Z49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="AA5" s="43">
         <f>'Fuel Type'!AA49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="AB5" s="43">
         <f>'Fuel Type'!AB49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="AC5" s="43">
         <f>'Fuel Type'!AC49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="AD5" s="43">
         <f>'Fuel Type'!AD49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="AE5" s="43">
         <f>'Fuel Type'!AE49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="AF5" s="43">
         <f>'Fuel Type'!AF49</f>
-        <v>0</v>
+        <v>806.45161290322585</v>
       </c>
       <c r="AG5" s="43">
         <f>'Fuel Type'!AG49</f>
@@ -20337,127 +20643,127 @@
       </c>
       <c r="B6" s="43">
         <f>'Fuel Type'!B50</f>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="C6" s="43">
         <f>'Fuel Type'!C50</f>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="D6" s="43">
         <f>'Fuel Type'!D50</f>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="E6" s="43">
         <f>'Fuel Type'!E50</f>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="F6" s="43">
         <f>'Fuel Type'!F50</f>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="G6" s="43">
         <f>'Fuel Type'!G50</f>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="H6" s="43">
         <f>'Fuel Type'!H50</f>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="I6" s="43">
         <f>'Fuel Type'!I50</f>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="J6" s="43">
         <f>'Fuel Type'!J50</f>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="K6" s="43">
         <f>'Fuel Type'!K50</f>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="L6" s="43">
         <f>'Fuel Type'!L50</f>
-        <v>3.8061870792883794</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="M6" s="43">
         <f>'Fuel Type'!M50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="N6" s="43">
         <f>'Fuel Type'!N50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="O6" s="43">
         <f>'Fuel Type'!O50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="P6" s="43">
         <f>'Fuel Type'!P50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="Q6" s="43">
         <f>'Fuel Type'!Q50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="R6" s="43">
         <f>'Fuel Type'!R50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="S6" s="43">
         <f>'Fuel Type'!S50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="T6" s="43">
         <f>'Fuel Type'!T50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="U6" s="43">
         <f>'Fuel Type'!U50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="V6" s="43">
         <f>'Fuel Type'!V50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="W6" s="43">
         <f>'Fuel Type'!W50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="X6" s="43">
         <f>'Fuel Type'!X50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="Y6" s="43">
         <f>'Fuel Type'!Y50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="Z6" s="43">
         <f>'Fuel Type'!Z50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="AA6" s="43">
         <f>'Fuel Type'!AA50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="AB6" s="43">
         <f>'Fuel Type'!AB50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="AC6" s="43">
         <f>'Fuel Type'!AC50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="AD6" s="43">
         <f>'Fuel Type'!AD50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="AE6" s="43">
         <f>'Fuel Type'!AE50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="AF6" s="43">
         <f>'Fuel Type'!AF50</f>
-        <v>0</v>
+        <v>483.87096774193549</v>
       </c>
       <c r="AG6" s="43">
         <f>'Fuel Type'!AG50</f>
@@ -20546,127 +20852,127 @@
       </c>
       <c r="B7" s="43">
         <f>'Fuel Type'!B51</f>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="C7" s="43">
         <f>'Fuel Type'!C51</f>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="D7" s="43">
         <f>'Fuel Type'!D51</f>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="E7" s="43">
         <f>'Fuel Type'!E51</f>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="F7" s="43">
         <f>'Fuel Type'!F51</f>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="G7" s="43">
         <f>'Fuel Type'!G51</f>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="H7" s="43">
         <f>'Fuel Type'!H51</f>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="I7" s="43">
         <f>'Fuel Type'!I51</f>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="J7" s="43">
         <f>'Fuel Type'!J51</f>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="K7" s="43">
         <f>'Fuel Type'!K51</f>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="L7" s="43">
         <f>'Fuel Type'!L51</f>
-        <v>413.0554545454545</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="M7" s="43">
         <f>'Fuel Type'!M51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="N7" s="43">
         <f>'Fuel Type'!N51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="O7" s="43">
         <f>'Fuel Type'!O51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="P7" s="43">
         <f>'Fuel Type'!P51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="Q7" s="43">
         <f>'Fuel Type'!Q51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="R7" s="43">
         <f>'Fuel Type'!R51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="S7" s="43">
         <f>'Fuel Type'!S51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="T7" s="43">
         <f>'Fuel Type'!T51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="U7" s="43">
         <f>'Fuel Type'!U51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="V7" s="43">
         <f>'Fuel Type'!V51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="W7" s="43">
         <f>'Fuel Type'!W51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="X7" s="43">
         <f>'Fuel Type'!X51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="Y7" s="43">
         <f>'Fuel Type'!Y51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="Z7" s="43">
         <f>'Fuel Type'!Z51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="AA7" s="43">
         <f>'Fuel Type'!AA51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="AB7" s="43">
         <f>'Fuel Type'!AB51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="AC7" s="43">
         <f>'Fuel Type'!AC51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="AD7" s="43">
         <f>'Fuel Type'!AD51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="AE7" s="43">
         <f>'Fuel Type'!AE51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="AF7" s="43">
         <f>'Fuel Type'!AF51</f>
-        <v>0</v>
+        <v>870.9677419354839</v>
       </c>
       <c r="AG7" s="43">
         <f>'Fuel Type'!AG51</f>
@@ -20953,127 +21259,127 @@
       </c>
       <c r="B9" s="43">
         <f>'Fuel Type'!B53</f>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="C9" s="43">
         <f>'Fuel Type'!C53</f>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="D9" s="43">
         <f>'Fuel Type'!D53</f>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="E9" s="43">
         <f>'Fuel Type'!E53</f>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="F9" s="43">
         <f>'Fuel Type'!F53</f>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="G9" s="43">
         <f>'Fuel Type'!G53</f>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="H9" s="43">
         <f>'Fuel Type'!H53</f>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="I9" s="43">
         <f>'Fuel Type'!I53</f>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="J9" s="43">
         <f>'Fuel Type'!J53</f>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="K9" s="43">
         <f>'Fuel Type'!K53</f>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="L9" s="43">
         <f>'Fuel Type'!L53</f>
-        <v>79.997655303170703</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="M9" s="43">
         <f>'Fuel Type'!M53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="N9" s="43">
         <f>'Fuel Type'!N53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="O9" s="43">
         <f>'Fuel Type'!O53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="P9" s="43">
         <f>'Fuel Type'!P53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="Q9" s="43">
         <f>'Fuel Type'!Q53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="R9" s="43">
         <f>'Fuel Type'!R53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="S9" s="43">
         <f>'Fuel Type'!S53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="T9" s="43">
         <f>'Fuel Type'!T53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="U9" s="43">
         <f>'Fuel Type'!U53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="V9" s="43">
         <f>'Fuel Type'!V53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="W9" s="43">
         <f>'Fuel Type'!W53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="X9" s="43">
         <f>'Fuel Type'!X53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="Y9" s="43">
         <f>'Fuel Type'!Y53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="Z9" s="43">
         <f>'Fuel Type'!Z53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="AA9" s="43">
         <f>'Fuel Type'!AA53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="AB9" s="43">
         <f>'Fuel Type'!AB53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="AC9" s="43">
         <f>'Fuel Type'!AC53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="AD9" s="43">
         <f>'Fuel Type'!AD53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="AE9" s="43">
         <f>'Fuel Type'!AE53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="AF9" s="43">
         <f>'Fuel Type'!AF53</f>
-        <v>0</v>
+        <v>2.5805695259087322</v>
       </c>
       <c r="AG9" s="43">
         <f>'Fuel Type'!AG53</f>
@@ -21162,127 +21468,127 @@
       </c>
       <c r="B10" s="43">
         <f>'Fuel Type'!B54</f>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="C10" s="43">
         <f>'Fuel Type'!C54</f>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="D10" s="43">
         <f>'Fuel Type'!D54</f>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="E10" s="43">
         <f>'Fuel Type'!E54</f>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="F10" s="43">
         <f>'Fuel Type'!F54</f>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="G10" s="43">
         <f>'Fuel Type'!G54</f>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="H10" s="43">
         <f>'Fuel Type'!H54</f>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="I10" s="43">
         <f>'Fuel Type'!I54</f>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="J10" s="43">
         <f>'Fuel Type'!J54</f>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="K10" s="43">
         <f>'Fuel Type'!K54</f>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="L10" s="43">
         <f>'Fuel Type'!L54</f>
-        <v>305</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="M10" s="43">
         <f>'Fuel Type'!M54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="N10" s="43">
         <f>'Fuel Type'!N54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="O10" s="43">
         <f>'Fuel Type'!O54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="P10" s="43">
         <f>'Fuel Type'!P54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="Q10" s="43">
         <f>'Fuel Type'!Q54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="R10" s="43">
         <f>'Fuel Type'!R54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="S10" s="43">
         <f>'Fuel Type'!S54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="T10" s="43">
         <f>'Fuel Type'!T54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="U10" s="43">
         <f>'Fuel Type'!U54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="V10" s="43">
         <f>'Fuel Type'!V54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="W10" s="43">
         <f>'Fuel Type'!W54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="X10" s="43">
         <f>'Fuel Type'!X54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="Y10" s="43">
         <f>'Fuel Type'!Y54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="Z10" s="43">
         <f>'Fuel Type'!Z54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="AA10" s="43">
         <f>'Fuel Type'!AA54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="AB10" s="43">
         <f>'Fuel Type'!AB54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="AC10" s="43">
         <f>'Fuel Type'!AC54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="AD10" s="43">
         <f>'Fuel Type'!AD54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="AE10" s="43">
         <f>'Fuel Type'!AE54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="AF10" s="43">
         <f>'Fuel Type'!AF54</f>
-        <v>0</v>
+        <v>9.8387096774193541</v>
       </c>
       <c r="AG10" s="43">
         <f>'Fuel Type'!AG54</f>
@@ -22625,127 +22931,127 @@
       </c>
       <c r="B17" s="43">
         <f>'Fuel Type'!B61</f>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="C17" s="43">
         <f>'Fuel Type'!C61</f>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="D17" s="43">
         <f>'Fuel Type'!D61</f>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="E17" s="43">
         <f>'Fuel Type'!E61</f>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="F17" s="43">
         <f>'Fuel Type'!F61</f>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="G17" s="43">
         <f>'Fuel Type'!G61</f>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="H17" s="43">
         <f>'Fuel Type'!H61</f>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="I17" s="43">
         <f>'Fuel Type'!I61</f>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="J17" s="43">
         <f>'Fuel Type'!J61</f>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="K17" s="43">
         <f>'Fuel Type'!K61</f>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="L17" s="43">
         <f>'Fuel Type'!L61</f>
-        <v>0.91143560592020501</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="M17" s="43">
         <f>'Fuel Type'!M61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="N17" s="43">
         <f>'Fuel Type'!N61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="O17" s="43">
         <f>'Fuel Type'!O61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="P17" s="43">
         <f>'Fuel Type'!P61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="Q17" s="43">
         <f>'Fuel Type'!Q61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="R17" s="43">
         <f>'Fuel Type'!R61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="S17" s="43">
         <f>'Fuel Type'!S61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="T17" s="43">
         <f>'Fuel Type'!T61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="U17" s="43">
         <f>'Fuel Type'!U61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="V17" s="43">
         <f>'Fuel Type'!V61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="W17" s="43">
         <f>'Fuel Type'!W61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="X17" s="43">
         <f>'Fuel Type'!X61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="Y17" s="43">
         <f>'Fuel Type'!Y61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="Z17" s="43">
         <f>'Fuel Type'!Z61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="AA17" s="43">
         <f>'Fuel Type'!AA61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="AB17" s="43">
         <f>'Fuel Type'!AB61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="AC17" s="43">
         <f>'Fuel Type'!AC61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="AD17" s="43">
         <f>'Fuel Type'!AD61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="AE17" s="43">
         <f>'Fuel Type'!AE61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="AF17" s="43">
         <f>'Fuel Type'!AF61</f>
-        <v>0</v>
+        <v>2.9401148578071128E-2</v>
       </c>
       <c r="AG17" s="43">
         <f>'Fuel Type'!AG61</f>

--- a/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/BPMCCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EBB44A-9B6F-2743-9BDF-77757C7A5BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A8CB58-398E-F346-9596-AAF273111E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -954,8 +954,15 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -963,13 +970,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1257,13 +1257,13 @@
       <c r="A3" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="47" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="43"/>
-      <c r="B4" s="53">
+      <c r="B4" s="48">
         <v>2021</v>
       </c>
     </row>
@@ -1290,15 +1290,15 @@
       <c r="B9" s="39"/>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="47"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="44"/>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="47"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="44"/>
     </row>
     <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="47"/>
+      <c r="A12" s="49"/>
       <c r="B12" s="44"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -2309,20 +2309,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="41" t="s">
@@ -9341,40 +9341,40 @@
       </c>
     </row>
     <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="48" t="s">
+      <c r="B87" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="C87" s="49"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="49"/>
-      <c r="G87" s="49"/>
-      <c r="H87" s="49"/>
-      <c r="I87" s="49"/>
-      <c r="J87" s="49"/>
-      <c r="K87" s="49"/>
-      <c r="L87" s="49"/>
-      <c r="M87" s="49"/>
-      <c r="N87" s="49"/>
-      <c r="O87" s="49"/>
-      <c r="P87" s="49"/>
-      <c r="Q87" s="49"/>
-      <c r="R87" s="49"/>
-      <c r="S87" s="49"/>
-      <c r="T87" s="49"/>
-      <c r="U87" s="49"/>
-      <c r="V87" s="49"/>
-      <c r="W87" s="49"/>
-      <c r="X87" s="49"/>
-      <c r="Y87" s="49"/>
-      <c r="Z87" s="49"/>
-      <c r="AA87" s="49"/>
-      <c r="AB87" s="49"/>
-      <c r="AC87" s="49"/>
-      <c r="AD87" s="49"/>
-      <c r="AE87" s="49"/>
-      <c r="AF87" s="49"/>
-      <c r="AG87" s="49"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="52"/>
+      <c r="I87" s="52"/>
+      <c r="J87" s="52"/>
+      <c r="K87" s="52"/>
+      <c r="L87" s="52"/>
+      <c r="M87" s="52"/>
+      <c r="N87" s="52"/>
+      <c r="O87" s="52"/>
+      <c r="P87" s="52"/>
+      <c r="Q87" s="52"/>
+      <c r="R87" s="52"/>
+      <c r="S87" s="52"/>
+      <c r="T87" s="52"/>
+      <c r="U87" s="52"/>
+      <c r="V87" s="52"/>
+      <c r="W87" s="52"/>
+      <c r="X87" s="52"/>
+      <c r="Y87" s="52"/>
+      <c r="Z87" s="52"/>
+      <c r="AA87" s="52"/>
+      <c r="AB87" s="52"/>
+      <c r="AC87" s="52"/>
+      <c r="AD87" s="52"/>
+      <c r="AE87" s="52"/>
+      <c r="AF87" s="52"/>
+      <c r="AG87" s="52"/>
       <c r="AH87" s="21"/>
     </row>
     <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9498,39 +9498,39 @@
       </c>
     </row>
     <row r="112" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="50"/>
-      <c r="C112" s="51"/>
-      <c r="D112" s="51"/>
-      <c r="E112" s="51"/>
-      <c r="F112" s="51"/>
-      <c r="G112" s="51"/>
-      <c r="H112" s="51"/>
-      <c r="I112" s="51"/>
-      <c r="J112" s="51"/>
-      <c r="K112" s="51"/>
-      <c r="L112" s="51"/>
-      <c r="M112" s="51"/>
-      <c r="N112" s="51"/>
-      <c r="O112" s="51"/>
-      <c r="P112" s="51"/>
-      <c r="Q112" s="51"/>
-      <c r="R112" s="51"/>
-      <c r="S112" s="51"/>
-      <c r="T112" s="51"/>
-      <c r="U112" s="51"/>
-      <c r="V112" s="51"/>
-      <c r="W112" s="51"/>
-      <c r="X112" s="51"/>
-      <c r="Y112" s="51"/>
-      <c r="Z112" s="51"/>
-      <c r="AA112" s="51"/>
-      <c r="AB112" s="51"/>
-      <c r="AC112" s="51"/>
-      <c r="AD112" s="51"/>
-      <c r="AE112" s="51"/>
-      <c r="AF112" s="51"/>
-      <c r="AG112" s="51"/>
-      <c r="AH112" s="51"/>
+      <c r="B112" s="53"/>
+      <c r="C112" s="54"/>
+      <c r="D112" s="54"/>
+      <c r="E112" s="54"/>
+      <c r="F112" s="54"/>
+      <c r="G112" s="54"/>
+      <c r="H112" s="54"/>
+      <c r="I112" s="54"/>
+      <c r="J112" s="54"/>
+      <c r="K112" s="54"/>
+      <c r="L112" s="54"/>
+      <c r="M112" s="54"/>
+      <c r="N112" s="54"/>
+      <c r="O112" s="54"/>
+      <c r="P112" s="54"/>
+      <c r="Q112" s="54"/>
+      <c r="R112" s="54"/>
+      <c r="S112" s="54"/>
+      <c r="T112" s="54"/>
+      <c r="U112" s="54"/>
+      <c r="V112" s="54"/>
+      <c r="W112" s="54"/>
+      <c r="X112" s="54"/>
+      <c r="Y112" s="54"/>
+      <c r="Z112" s="54"/>
+      <c r="AA112" s="54"/>
+      <c r="AB112" s="54"/>
+      <c r="AC112" s="54"/>
+      <c r="AD112" s="54"/>
+      <c r="AE112" s="54"/>
+      <c r="AF112" s="54"/>
+      <c r="AG112" s="54"/>
+      <c r="AH112" s="54"/>
     </row>
     <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -9728,39 +9728,39 @@
     <row r="306" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="307" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="308" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B308" s="50"/>
-      <c r="C308" s="51"/>
-      <c r="D308" s="51"/>
-      <c r="E308" s="51"/>
-      <c r="F308" s="51"/>
-      <c r="G308" s="51"/>
-      <c r="H308" s="51"/>
-      <c r="I308" s="51"/>
-      <c r="J308" s="51"/>
-      <c r="K308" s="51"/>
-      <c r="L308" s="51"/>
-      <c r="M308" s="51"/>
-      <c r="N308" s="51"/>
-      <c r="O308" s="51"/>
-      <c r="P308" s="51"/>
-      <c r="Q308" s="51"/>
-      <c r="R308" s="51"/>
-      <c r="S308" s="51"/>
-      <c r="T308" s="51"/>
-      <c r="U308" s="51"/>
-      <c r="V308" s="51"/>
-      <c r="W308" s="51"/>
-      <c r="X308" s="51"/>
-      <c r="Y308" s="51"/>
-      <c r="Z308" s="51"/>
-      <c r="AA308" s="51"/>
-      <c r="AB308" s="51"/>
-      <c r="AC308" s="51"/>
-      <c r="AD308" s="51"/>
-      <c r="AE308" s="51"/>
-      <c r="AF308" s="51"/>
-      <c r="AG308" s="51"/>
-      <c r="AH308" s="51"/>
+      <c r="B308" s="53"/>
+      <c r="C308" s="54"/>
+      <c r="D308" s="54"/>
+      <c r="E308" s="54"/>
+      <c r="F308" s="54"/>
+      <c r="G308" s="54"/>
+      <c r="H308" s="54"/>
+      <c r="I308" s="54"/>
+      <c r="J308" s="54"/>
+      <c r="K308" s="54"/>
+      <c r="L308" s="54"/>
+      <c r="M308" s="54"/>
+      <c r="N308" s="54"/>
+      <c r="O308" s="54"/>
+      <c r="P308" s="54"/>
+      <c r="Q308" s="54"/>
+      <c r="R308" s="54"/>
+      <c r="S308" s="54"/>
+      <c r="T308" s="54"/>
+      <c r="U308" s="54"/>
+      <c r="V308" s="54"/>
+      <c r="W308" s="54"/>
+      <c r="X308" s="54"/>
+      <c r="Y308" s="54"/>
+      <c r="Z308" s="54"/>
+      <c r="AA308" s="54"/>
+      <c r="AB308" s="54"/>
+      <c r="AC308" s="54"/>
+      <c r="AD308" s="54"/>
+      <c r="AE308" s="54"/>
+      <c r="AF308" s="54"/>
+      <c r="AG308" s="54"/>
+      <c r="AH308" s="54"/>
     </row>
     <row r="309" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="310" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
